--- a/test-case-exports/QRPayment.xlsx
+++ b/test-case-exports/QRPayment.xlsx
@@ -245,7 +245,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-09-08T15:08:53.588Z</t>
+    <t>2026-09-09T06:44:10.178Z</t>
   </si>
   <si>
     <t>Total test cases</t>
